--- a/R/data/df_persona_per_group.xlsx
+++ b/R/data/df_persona_per_group.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D2">
-        <v>915</v>
+        <v>1078</v>
       </c>
       <c r="E2">
-        <v>0.5669999999999999</v>
+        <v>0.482</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -595,31 +595,31 @@
         <v>20</v>
       </c>
       <c r="S2">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="T2">
-        <v>32.4</v>
+        <v>34.3</v>
       </c>
       <c r="U2">
+        <v>6.5</v>
+      </c>
+      <c r="V2">
+        <v>6.5</v>
+      </c>
+      <c r="W2">
+        <v>6.1</v>
+      </c>
+      <c r="X2">
         <v>6.4</v>
       </c>
-      <c r="V2">
-        <v>6.4</v>
-      </c>
-      <c r="W2">
-        <v>5.9</v>
-      </c>
-      <c r="X2">
-        <v>6.3</v>
-      </c>
       <c r="Y2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z2">
         <v>6.2</v>
       </c>
       <c r="AA2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D3">
-        <v>698</v>
+        <v>1159</v>
       </c>
       <c r="E3">
-        <v>0.433</v>
+        <v>0.518</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HAVO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EM&amp;CM</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -715,31 +715,31 @@
         <v>19</v>
       </c>
       <c r="S3">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="T3">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="U3">
+        <v>6.5</v>
+      </c>
+      <c r="V3">
+        <v>6.5</v>
+      </c>
+      <c r="W3">
+        <v>6.1</v>
+      </c>
+      <c r="X3">
         <v>6.4</v>
       </c>
-      <c r="V3">
-        <v>6.4</v>
-      </c>
-      <c r="W3">
-        <v>5.9</v>
-      </c>
-      <c r="X3">
-        <v>6.3</v>
-      </c>
       <c r="Y3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z3">
         <v>6.2</v>
       </c>
       <c r="AA3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AB3">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>2017</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="4">
@@ -763,17 +763,17 @@
         </is>
       </c>
       <c r="C4">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D4">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E4">
-        <v>0.469</v>
+        <v>0.338</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MedV</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -835,31 +835,31 @@
         <v>19</v>
       </c>
       <c r="S4">
-        <v>137.5</v>
+        <v>154</v>
       </c>
       <c r="T4">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="U4">
+        <v>6.5</v>
+      </c>
+      <c r="V4">
+        <v>6.5</v>
+      </c>
+      <c r="W4">
+        <v>6.1</v>
+      </c>
+      <c r="X4">
         <v>6.4</v>
       </c>
-      <c r="V4">
-        <v>6.4</v>
-      </c>
-      <c r="W4">
-        <v>5.9</v>
-      </c>
-      <c r="X4">
-        <v>6.3</v>
-      </c>
       <c r="Y4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z4">
         <v>6.2</v>
       </c>
       <c r="AA4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2016</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="5">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D5">
-        <v>176</v>
+        <v>311</v>
       </c>
       <c r="E5">
-        <v>0.109</v>
+        <v>0.139</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -903,17 +903,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HAVO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MedV</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -952,34 +952,34 @@
         </is>
       </c>
       <c r="R5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S5">
-        <v>134.5</v>
+        <v>162</v>
       </c>
       <c r="T5">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="U5">
+        <v>6.5</v>
+      </c>
+      <c r="V5">
+        <v>6.5</v>
+      </c>
+      <c r="W5">
+        <v>6.1</v>
+      </c>
+      <c r="X5">
         <v>6.4</v>
       </c>
-      <c r="V5">
-        <v>6.4</v>
-      </c>
-      <c r="W5">
-        <v>5.9</v>
-      </c>
-      <c r="X5">
-        <v>6.3</v>
-      </c>
       <c r="Y5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z5">
         <v>6.2</v>
       </c>
       <c r="AA5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="6">
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D6">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="E6">
-        <v>0.125</v>
+        <v>0.108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EM&amp;CM</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1038,22 +1038,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1075,25 +1075,25 @@
         <v>21</v>
       </c>
       <c r="S6">
-        <v>128.5</v>
+        <v>124</v>
       </c>
       <c r="T6">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="U6">
+        <v>6.5</v>
+      </c>
+      <c r="V6">
+        <v>6.5</v>
+      </c>
+      <c r="W6">
+        <v>6.1</v>
+      </c>
+      <c r="X6">
         <v>6.4</v>
       </c>
-      <c r="V6">
-        <v>6.4</v>
-      </c>
-      <c r="W6">
-        <v>5.9</v>
-      </c>
-      <c r="X6">
-        <v>6.3</v>
-      </c>
       <c r="Y6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z6">
         <v>6.2</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="7">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D7">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="E7">
-        <v>0.276</v>
+        <v>0.184</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1192,28 +1192,28 @@
         </is>
       </c>
       <c r="R7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S7">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="T7">
-        <v>36.1</v>
+        <v>34.2</v>
       </c>
       <c r="U7">
+        <v>6.5</v>
+      </c>
+      <c r="V7">
+        <v>6.5</v>
+      </c>
+      <c r="W7">
+        <v>6.1</v>
+      </c>
+      <c r="X7">
         <v>6.4</v>
       </c>
-      <c r="V7">
-        <v>6.4</v>
-      </c>
-      <c r="W7">
-        <v>5.9</v>
-      </c>
-      <c r="X7">
-        <v>6.3</v>
-      </c>
       <c r="Y7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z7">
         <v>6.2</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>2015</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="8">
@@ -1243,17 +1243,17 @@
         </is>
       </c>
       <c r="C8">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1312,28 +1312,28 @@
         </is>
       </c>
       <c r="R8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S8">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="T8">
-        <v>29.8</v>
+        <v>26.8</v>
       </c>
       <c r="U8">
+        <v>6.5</v>
+      </c>
+      <c r="V8">
+        <v>6.5</v>
+      </c>
+      <c r="W8">
+        <v>6.1</v>
+      </c>
+      <c r="X8">
         <v>6.4</v>
       </c>
-      <c r="V8">
-        <v>6.4</v>
-      </c>
-      <c r="W8">
-        <v>5.9</v>
-      </c>
-      <c r="X8">
-        <v>6.3</v>
-      </c>
       <c r="Y8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z8">
         <v>6.2</v>
@@ -1342,13 +1342,13 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>2019</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="9">
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EM&amp;CM</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1435,25 +1435,25 @@
         <v>22</v>
       </c>
       <c r="S9">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T9">
-        <v>30.5</v>
+        <v>29.7</v>
       </c>
       <c r="U9">
+        <v>6.5</v>
+      </c>
+      <c r="V9">
+        <v>6.5</v>
+      </c>
+      <c r="W9">
+        <v>6.1</v>
+      </c>
+      <c r="X9">
         <v>6.4</v>
       </c>
-      <c r="V9">
-        <v>6.4</v>
-      </c>
-      <c r="W9">
-        <v>5.9</v>
-      </c>
-      <c r="X9">
-        <v>6.3</v>
-      </c>
       <c r="Y9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z9">
         <v>6.2</v>
@@ -1468,52 +1468,52 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>2012</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vooropleiding</t>
+          <t>Aansluiting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Overig</t>
         </is>
       </c>
       <c r="C10">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D10">
-        <v>522</v>
+        <v>197</v>
       </c>
       <c r="E10">
-        <v>0.324</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Overig</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MedV</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1555,25 +1555,25 @@
         <v>21</v>
       </c>
       <c r="S10">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="T10">
-        <v>32.7</v>
+        <v>34.3</v>
       </c>
       <c r="U10">
+        <v>6.5</v>
+      </c>
+      <c r="V10">
+        <v>6.5</v>
+      </c>
+      <c r="W10">
+        <v>6.1</v>
+      </c>
+      <c r="X10">
         <v>6.4</v>
       </c>
-      <c r="V10">
-        <v>6.4</v>
-      </c>
-      <c r="W10">
-        <v>5.9</v>
-      </c>
-      <c r="X10">
-        <v>6.3</v>
-      </c>
       <c r="Y10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z10">
         <v>6.2</v>
@@ -1588,77 +1588,77 @@
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>2017</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vooropleiding</t>
+          <t>Aansluiting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HAVO</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="C11">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D11">
-        <v>860</v>
+        <v>276</v>
       </c>
       <c r="E11">
-        <v>0.533</v>
+        <v>0.123</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HAVO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EM&amp;CM</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1675,31 +1675,31 @@
         <v>19</v>
       </c>
       <c r="S11">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="T11">
-        <v>35.9</v>
+        <v>34.3</v>
       </c>
       <c r="U11">
+        <v>6.5</v>
+      </c>
+      <c r="V11">
+        <v>6.5</v>
+      </c>
+      <c r="W11">
+        <v>6.1</v>
+      </c>
+      <c r="X11">
         <v>6.4</v>
       </c>
-      <c r="V11">
-        <v>6.4</v>
-      </c>
-      <c r="W11">
-        <v>5.9</v>
-      </c>
-      <c r="X11">
-        <v>6.3</v>
-      </c>
       <c r="Y11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z11">
         <v>6.2</v>
       </c>
       <c r="AA11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>2016</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="12">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="C12">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D12">
-        <v>58</v>
+        <v>534</v>
       </c>
       <c r="E12">
-        <v>0.036</v>
+        <v>0.239</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Switch extern</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1758,27 +1758,27 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1792,34 +1792,34 @@
         </is>
       </c>
       <c r="R12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S12">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="T12">
-        <v>30.9</v>
+        <v>32.7</v>
       </c>
       <c r="U12">
+        <v>6.5</v>
+      </c>
+      <c r="V12">
+        <v>6.5</v>
+      </c>
+      <c r="W12">
+        <v>6.1</v>
+      </c>
+      <c r="X12">
         <v>6.4</v>
       </c>
-      <c r="V12">
-        <v>6.4</v>
-      </c>
-      <c r="W12">
-        <v>5.9</v>
-      </c>
-      <c r="X12">
-        <v>6.3</v>
-      </c>
       <c r="Y12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z12">
         <v>6.2</v>
       </c>
       <c r="AA12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AB12">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>2016</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="13">
@@ -1839,17 +1839,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>HAVO</t>
         </is>
       </c>
       <c r="C13">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D13">
-        <v>92</v>
+        <v>733</v>
       </c>
       <c r="E13">
-        <v>0.057</v>
+        <v>0.328</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>HAVO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1873,32 +1873,32 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1912,43 +1912,43 @@
         </is>
       </c>
       <c r="R13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S13">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="T13">
-        <v>15.5</v>
+        <v>34.3</v>
       </c>
       <c r="U13">
+        <v>6.5</v>
+      </c>
+      <c r="V13">
+        <v>6.5</v>
+      </c>
+      <c r="W13">
+        <v>6.1</v>
+      </c>
+      <c r="X13">
         <v>6.4</v>
       </c>
-      <c r="V13">
-        <v>6.4</v>
-      </c>
-      <c r="W13">
-        <v>5.9</v>
-      </c>
-      <c r="X13">
-        <v>6.3</v>
-      </c>
       <c r="Y13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z13">
         <v>6.2</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AC13">
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="14">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C14">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="E14">
-        <v>0.019</v>
+        <v>0.051</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1978,17 +1978,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Na CD</t>
+          <t>Switch extern</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1998,27 +1998,27 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2032,43 +2032,43 @@
         </is>
       </c>
       <c r="R14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S14">
-        <v>127.5</v>
+        <v>133</v>
       </c>
       <c r="T14">
-        <v>29.6</v>
+        <v>34.3</v>
       </c>
       <c r="U14">
+        <v>6.5</v>
+      </c>
+      <c r="V14">
+        <v>6.5</v>
+      </c>
+      <c r="W14">
+        <v>6.1</v>
+      </c>
+      <c r="X14">
         <v>6.4</v>
       </c>
-      <c r="V14">
-        <v>6.4</v>
-      </c>
-      <c r="W14">
-        <v>5.9</v>
-      </c>
-      <c r="X14">
-        <v>6.3</v>
-      </c>
       <c r="Y14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z14">
         <v>6.2</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AB14">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="AC14">
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>2017.5</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="15">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="C15">
-        <v>1613</v>
+        <v>2237</v>
       </c>
       <c r="D15">
-        <v>51</v>
+        <v>749</v>
       </c>
       <c r="E15">
-        <v>0.032</v>
+        <v>0.335</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Switch extern</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Onbekend</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2155,40 +2155,400 @@
         <v>20</v>
       </c>
       <c r="S15">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="T15">
-        <v>38.3</v>
+        <v>34.3</v>
       </c>
       <c r="U15">
+        <v>6.5</v>
+      </c>
+      <c r="V15">
+        <v>6.5</v>
+      </c>
+      <c r="W15">
+        <v>6.1</v>
+      </c>
+      <c r="X15">
         <v>6.4</v>
       </c>
-      <c r="V15">
-        <v>6.4</v>
-      </c>
-      <c r="W15">
-        <v>5.9</v>
-      </c>
-      <c r="X15">
-        <v>6.3</v>
-      </c>
       <c r="Y15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z15">
         <v>6.2</v>
       </c>
       <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vooropleiding</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>2237</v>
+      </c>
+      <c r="D16">
+        <v>43</v>
+      </c>
+      <c r="E16">
+        <v>0.019</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Na CD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R16">
+        <v>22</v>
+      </c>
+      <c r="S16">
+        <v>127</v>
+      </c>
+      <c r="T16">
+        <v>27.3</v>
+      </c>
+      <c r="U16">
+        <v>6.5</v>
+      </c>
+      <c r="V16">
+        <v>6.5</v>
+      </c>
+      <c r="W16">
+        <v>6.1</v>
+      </c>
+      <c r="X16">
+        <v>6.4</v>
+      </c>
+      <c r="Y16">
+        <v>7.2</v>
+      </c>
+      <c r="Z16">
+        <v>6.2</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Vooropleiding</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>2237</v>
+      </c>
+      <c r="D17">
+        <v>57</v>
+      </c>
+      <c r="E17">
+        <v>0.025</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Switch extern</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R17">
+        <v>21</v>
+      </c>
+      <c r="S17">
+        <v>125</v>
+      </c>
+      <c r="T17">
+        <v>34.3</v>
+      </c>
+      <c r="U17">
+        <v>6.5</v>
+      </c>
+      <c r="V17">
+        <v>6.5</v>
+      </c>
+      <c r="W17">
+        <v>6.1</v>
+      </c>
+      <c r="X17">
+        <v>6.4</v>
+      </c>
+      <c r="Y17">
+        <v>7.2</v>
+      </c>
+      <c r="Z17">
+        <v>6.2</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vooropleiding</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Overig</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>2237</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>0.003</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Switch extern</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Overig</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R18">
+        <v>20</v>
+      </c>
+      <c r="S18">
+        <v>130.5</v>
+      </c>
+      <c r="T18">
+        <v>31</v>
+      </c>
+      <c r="U18">
+        <v>6.5</v>
+      </c>
+      <c r="V18">
+        <v>6.5</v>
+      </c>
+      <c r="W18">
+        <v>6.1</v>
+      </c>
+      <c r="X18">
+        <v>6.4</v>
+      </c>
+      <c r="Y18">
+        <v>7.2</v>
+      </c>
+      <c r="Z18">
+        <v>6.2</v>
+      </c>
+      <c r="AA18">
+        <v>0.2</v>
+      </c>
+      <c r="AB18">
         <v>0.1</v>
       </c>
-      <c r="AB15">
-        <v>0.1</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>2015</v>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>2018</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/df_persona_per_group.xlsx
+++ b/R/data/df_persona_per_group.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,70 +397,115 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Studiekeuzeprofiel</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>APCG</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Cijfer_CE_VO_missing</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cijfer_SE_VO_missing</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cijfer_CE_Nederlands_missing</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Cijfer_CE_Engels_missing</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Cijfer_CE_Wiskunde_missing</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Cijfer_CE_Natuurkunde_missing</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Dubbele_studie</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Leeftijd</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Aanmelding</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Reistijd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Cijfer_CE_VO</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Cijfer_SE_VO</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Cijfer_CE_Nederlands</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Cijfer_CE_Wiskunde</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Cijfer_CE_Engels</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Cijfer_CE_Natuurkunde</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SES_Totaal</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SES_Welvaart</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SES_Arbeid</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Collegejaar</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -478,13 +523,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D2">
-        <v>3209</v>
+        <v>915</v>
       </c>
       <c r="E2">
-        <v>0.647</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -503,7 +548,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -511,38 +556,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K2">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R2">
         <v>20</v>
       </c>
-      <c r="L2">
-        <v>52.6</v>
-      </c>
-      <c r="M2">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N2">
-        <v>57.5</v>
-      </c>
-      <c r="O2">
-        <v>60.7</v>
-      </c>
-      <c r="P2">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q2">
-        <v>58.9</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
       <c r="S2">
-        <v>-0</v>
+        <v>126</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="U2">
-        <v>2010</v>
+        <v>6.4</v>
+      </c>
+      <c r="V2">
+        <v>6.4</v>
+      </c>
+      <c r="W2">
+        <v>5.9</v>
+      </c>
+      <c r="X2">
+        <v>6.3</v>
+      </c>
+      <c r="Y2">
+        <v>7</v>
+      </c>
+      <c r="Z2">
+        <v>6.2</v>
+      </c>
+      <c r="AA2">
+        <v>0.1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>2016</v>
       </c>
     </row>
     <row r="3">
@@ -557,13 +643,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D3">
-        <v>1747</v>
+        <v>698</v>
       </c>
       <c r="E3">
-        <v>0.353</v>
+        <v>0.433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -582,7 +668,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM&amp;CM</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,38 +676,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K3">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R3">
         <v>19</v>
       </c>
-      <c r="L3">
-        <v>52.6</v>
-      </c>
-      <c r="M3">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N3">
-        <v>57.5</v>
-      </c>
-      <c r="O3">
-        <v>60.7</v>
-      </c>
-      <c r="P3">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q3">
-        <v>58.9</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3">
-        <v>-0</v>
+        <v>137</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>33.4</v>
       </c>
       <c r="U3">
-        <v>2014</v>
+        <v>6.4</v>
+      </c>
+      <c r="V3">
+        <v>6.4</v>
+      </c>
+      <c r="W3">
+        <v>5.9</v>
+      </c>
+      <c r="X3">
+        <v>6.3</v>
+      </c>
+      <c r="Y3">
+        <v>7</v>
+      </c>
+      <c r="Z3">
+        <v>6.2</v>
+      </c>
+      <c r="AA3">
+        <v>0.1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>2017</v>
       </c>
     </row>
     <row r="4">
@@ -636,13 +763,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D4">
-        <v>1696</v>
+        <v>756</v>
       </c>
       <c r="E4">
-        <v>0.342</v>
+        <v>0.469</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -661,7 +788,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>MedV</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -669,38 +796,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K4">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R4">
         <v>19</v>
       </c>
-      <c r="L4">
-        <v>52.6</v>
-      </c>
-      <c r="M4">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N4">
-        <v>57.5</v>
-      </c>
-      <c r="O4">
-        <v>60.7</v>
-      </c>
-      <c r="P4">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q4">
-        <v>58.9</v>
-      </c>
-      <c r="R4">
+      <c r="S4">
+        <v>137.5</v>
+      </c>
+      <c r="T4">
+        <v>34.2</v>
+      </c>
+      <c r="U4">
+        <v>6.4</v>
+      </c>
+      <c r="V4">
+        <v>6.4</v>
+      </c>
+      <c r="W4">
+        <v>5.9</v>
+      </c>
+      <c r="X4">
+        <v>6.3</v>
+      </c>
+      <c r="Y4">
+        <v>7</v>
+      </c>
+      <c r="Z4">
+        <v>6.2</v>
+      </c>
+      <c r="AA4">
         <v>0.1</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>2012</v>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>2016</v>
       </c>
     </row>
     <row r="5">
@@ -715,17 +883,17 @@
         </is>
       </c>
       <c r="C5">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D5">
-        <v>522</v>
+        <v>176</v>
       </c>
       <c r="E5">
-        <v>0.105</v>
+        <v>0.109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -735,12 +903,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>HAVO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>MedV</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -748,38 +916,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K5">
-        <v>21</v>
-      </c>
-      <c r="L5">
-        <v>52.6</v>
-      </c>
-      <c r="M5">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N5">
-        <v>57.5</v>
-      </c>
-      <c r="O5">
-        <v>60.7</v>
-      </c>
-      <c r="P5">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q5">
-        <v>58.9</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S5">
-        <v>-0</v>
+        <v>134.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>34.7</v>
       </c>
       <c r="U5">
-        <v>2016</v>
+        <v>6.4</v>
+      </c>
+      <c r="V5">
+        <v>6.4</v>
+      </c>
+      <c r="W5">
+        <v>5.9</v>
+      </c>
+      <c r="X5">
+        <v>6.3</v>
+      </c>
+      <c r="Y5">
+        <v>7</v>
+      </c>
+      <c r="Z5">
+        <v>6.2</v>
+      </c>
+      <c r="AA5">
+        <v>0.1</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>2017</v>
       </c>
     </row>
     <row r="6">
@@ -794,13 +1003,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D6">
-        <v>666</v>
+        <v>202</v>
       </c>
       <c r="E6">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -819,7 +1028,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM&amp;CM</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -827,38 +1036,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K6">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R6">
         <v>21</v>
       </c>
-      <c r="L6">
-        <v>52.6</v>
-      </c>
-      <c r="M6">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N6">
-        <v>57.5</v>
-      </c>
-      <c r="O6">
-        <v>60.7</v>
-      </c>
-      <c r="P6">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q6">
-        <v>58.9</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
       <c r="S6">
-        <v>-0</v>
+        <v>128.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="U6">
-        <v>2011</v>
+        <v>6.4</v>
+      </c>
+      <c r="V6">
+        <v>6.4</v>
+      </c>
+      <c r="W6">
+        <v>5.9</v>
+      </c>
+      <c r="X6">
+        <v>6.3</v>
+      </c>
+      <c r="Y6">
+        <v>7</v>
+      </c>
+      <c r="Z6">
+        <v>6.2</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>2018</v>
       </c>
     </row>
     <row r="7">
@@ -873,13 +1123,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D7">
-        <v>1463</v>
+        <v>445</v>
       </c>
       <c r="E7">
-        <v>0.295</v>
+        <v>0.276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -898,46 +1148,87 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="K7">
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R7">
         <v>20</v>
       </c>
-      <c r="L7">
-        <v>52.6</v>
-      </c>
-      <c r="M7">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N7">
-        <v>57.5</v>
-      </c>
-      <c r="O7">
-        <v>60.7</v>
-      </c>
-      <c r="P7">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q7">
-        <v>58.9</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
       <c r="S7">
-        <v>-0</v>
+        <v>112</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="U7">
-        <v>2012</v>
+        <v>6.4</v>
+      </c>
+      <c r="V7">
+        <v>6.4</v>
+      </c>
+      <c r="W7">
+        <v>5.9</v>
+      </c>
+      <c r="X7">
+        <v>6.3</v>
+      </c>
+      <c r="Y7">
+        <v>7</v>
+      </c>
+      <c r="Z7">
+        <v>6.2</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>2015</v>
       </c>
     </row>
     <row r="8">
@@ -952,13 +1243,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D8">
-        <v>430</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>0.08699999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -977,46 +1268,87 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>52.6</v>
-      </c>
-      <c r="M8">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N8">
-        <v>57.5</v>
-      </c>
-      <c r="O8">
-        <v>60.7</v>
-      </c>
-      <c r="P8">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q8">
-        <v>58.9</v>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S8">
+        <v>60</v>
+      </c>
+      <c r="T8">
+        <v>29.8</v>
+      </c>
+      <c r="U8">
+        <v>6.4</v>
+      </c>
+      <c r="V8">
+        <v>6.4</v>
+      </c>
+      <c r="W8">
+        <v>5.9</v>
+      </c>
+      <c r="X8">
+        <v>6.3</v>
+      </c>
+      <c r="Y8">
+        <v>7</v>
+      </c>
+      <c r="Z8">
+        <v>6.2</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
         <v>-0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>2010</v>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>2019</v>
       </c>
     </row>
     <row r="9">
@@ -1031,13 +1363,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D9">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>0.027</v>
+        <v>0.012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1056,7 +1388,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM&amp;CM</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1064,59 +1396,100 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K9">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="R9">
         <v>22</v>
       </c>
-      <c r="L9">
-        <v>52.6</v>
-      </c>
-      <c r="M9">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N9">
-        <v>57.5</v>
-      </c>
-      <c r="O9">
-        <v>60.7</v>
-      </c>
-      <c r="P9">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q9">
-        <v>58.9</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
       <c r="S9">
-        <v>-0</v>
+        <v>129</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="U9">
-        <v>2005</v>
+        <v>6.4</v>
+      </c>
+      <c r="V9">
+        <v>6.4</v>
+      </c>
+      <c r="W9">
+        <v>5.9</v>
+      </c>
+      <c r="X9">
+        <v>6.3</v>
+      </c>
+      <c r="Y9">
+        <v>7</v>
+      </c>
+      <c r="Z9">
+        <v>6.2</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>2012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aansluiting</t>
+          <t>Vooropleiding</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Overig</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="C10">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>522</v>
       </c>
       <c r="E10">
-        <v>0.008999999999999999</v>
+        <v>0.324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1125,7 +1498,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Overig</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1135,7 +1508,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>MedV</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1143,38 +1516,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K10">
-        <v>20</v>
-      </c>
-      <c r="L10">
-        <v>52.6</v>
-      </c>
-      <c r="M10">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N10">
-        <v>57.5</v>
-      </c>
-      <c r="O10">
-        <v>60.7</v>
-      </c>
-      <c r="P10">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q10">
-        <v>58.9</v>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S10">
-        <v>-0</v>
+        <v>127</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>32.7</v>
       </c>
       <c r="U10">
-        <v>2009</v>
+        <v>6.4</v>
+      </c>
+      <c r="V10">
+        <v>6.4</v>
+      </c>
+      <c r="W10">
+        <v>5.9</v>
+      </c>
+      <c r="X10">
+        <v>6.3</v>
+      </c>
+      <c r="Y10">
+        <v>7</v>
+      </c>
+      <c r="Z10">
+        <v>6.2</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>2017</v>
       </c>
     </row>
     <row r="11">
@@ -1185,17 +1599,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>HAVO</t>
         </is>
       </c>
       <c r="C11">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D11">
-        <v>1541</v>
+        <v>860</v>
       </c>
       <c r="E11">
-        <v>0.311</v>
+        <v>0.533</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1209,12 +1623,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>HAVO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM&amp;CM</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1222,38 +1636,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K11">
-        <v>21</v>
-      </c>
-      <c r="L11">
-        <v>52.6</v>
-      </c>
-      <c r="M11">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N11">
-        <v>57.5</v>
-      </c>
-      <c r="O11">
-        <v>60.7</v>
-      </c>
-      <c r="P11">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q11">
-        <v>58.9</v>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S11">
-        <v>-0</v>
+        <v>132</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>35.9</v>
       </c>
       <c r="U11">
-        <v>2011</v>
+        <v>6.4</v>
+      </c>
+      <c r="V11">
+        <v>6.4</v>
+      </c>
+      <c r="W11">
+        <v>5.9</v>
+      </c>
+      <c r="X11">
+        <v>6.3</v>
+      </c>
+      <c r="Y11">
+        <v>7</v>
+      </c>
+      <c r="Z11">
+        <v>6.2</v>
+      </c>
+      <c r="AA11">
+        <v>0.1</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>2016</v>
       </c>
     </row>
     <row r="12">
@@ -1264,17 +1719,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HAVO</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C12">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D12">
-        <v>2120</v>
+        <v>58</v>
       </c>
       <c r="E12">
-        <v>0.428</v>
+        <v>0.036</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1283,17 +1738,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Switch extern</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HAVO</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1301,38 +1756,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K12">
-        <v>18</v>
-      </c>
-      <c r="L12">
-        <v>52.6</v>
-      </c>
-      <c r="M12">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N12">
-        <v>57.5</v>
-      </c>
-      <c r="O12">
-        <v>60.7</v>
-      </c>
-      <c r="P12">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q12">
-        <v>58.9</v>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R12">
+        <v>19</v>
+      </c>
+      <c r="S12">
+        <v>132</v>
+      </c>
+      <c r="T12">
+        <v>30.9</v>
+      </c>
+      <c r="U12">
+        <v>6.4</v>
+      </c>
+      <c r="V12">
+        <v>6.4</v>
+      </c>
+      <c r="W12">
+        <v>5.9</v>
+      </c>
+      <c r="X12">
+        <v>6.3</v>
+      </c>
+      <c r="Y12">
+        <v>7</v>
+      </c>
+      <c r="Z12">
+        <v>6.2</v>
+      </c>
+      <c r="AA12">
         <v>0.1</v>
       </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>2011</v>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>2016</v>
       </c>
     </row>
     <row r="13">
@@ -1343,17 +1839,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="C13">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D13">
-        <v>319</v>
+        <v>92</v>
       </c>
       <c r="E13">
-        <v>0.064</v>
+        <v>0.057</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1362,56 +1858,97 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Switch extern</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nee</t>
-        </is>
-      </c>
-      <c r="K13">
-        <v>19</v>
-      </c>
-      <c r="L13">
-        <v>54.6</v>
-      </c>
-      <c r="M13">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N13">
-        <v>57.5</v>
-      </c>
-      <c r="O13">
-        <v>60.7</v>
-      </c>
-      <c r="P13">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q13">
-        <v>58.9</v>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S13">
-        <v>-0</v>
+        <v>126</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="U13">
-        <v>2009</v>
+        <v>6.4</v>
+      </c>
+      <c r="V13">
+        <v>6.4</v>
+      </c>
+      <c r="W13">
+        <v>5.9</v>
+      </c>
+      <c r="X13">
+        <v>6.3</v>
+      </c>
+      <c r="Y13">
+        <v>7</v>
+      </c>
+      <c r="Z13">
+        <v>6.2</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>2017</v>
       </c>
     </row>
     <row r="14">
@@ -1422,17 +1959,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C14">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D14">
-        <v>570</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>0.115</v>
+        <v>0.019</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1441,17 +1978,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tussenjaar</t>
+          <t>Na CD</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,38 +1996,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K14">
-        <v>20</v>
-      </c>
-      <c r="L14">
-        <v>52.6</v>
-      </c>
-      <c r="M14">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N14">
-        <v>57.5</v>
-      </c>
-      <c r="O14">
-        <v>60.7</v>
-      </c>
-      <c r="P14">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q14">
-        <v>58.9</v>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S14">
+        <v>127.5</v>
+      </c>
+      <c r="T14">
+        <v>29.6</v>
+      </c>
+      <c r="U14">
+        <v>6.4</v>
+      </c>
+      <c r="V14">
+        <v>6.4</v>
+      </c>
+      <c r="W14">
+        <v>5.9</v>
+      </c>
+      <c r="X14">
+        <v>6.3</v>
+      </c>
+      <c r="Y14">
+        <v>7</v>
+      </c>
+      <c r="Z14">
+        <v>6.2</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
         <v>-0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>2018</v>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>2017.5</v>
       </c>
     </row>
     <row r="15">
@@ -1501,36 +2079,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="C15">
-        <v>4956</v>
+        <v>1613</v>
       </c>
       <c r="D15">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="E15">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Na CD</t>
+          <t>Switch extern</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1538,275 +2116,79 @@
           <t>Nee</t>
         </is>
       </c>
-      <c r="K15">
-        <v>22</v>
-      </c>
-      <c r="L15">
-        <v>52.6</v>
-      </c>
-      <c r="M15">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N15">
-        <v>57.5</v>
-      </c>
-      <c r="O15">
-        <v>60.7</v>
-      </c>
-      <c r="P15">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q15">
-        <v>58.9</v>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S15">
-        <v>-0</v>
+        <v>128</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="U15">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vooropleiding</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>4956</v>
-      </c>
-      <c r="D16">
-        <v>232</v>
-      </c>
-      <c r="E16">
-        <v>0.047</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2e Studie</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
-      </c>
-      <c r="K16">
-        <v>22</v>
-      </c>
-      <c r="L16">
-        <v>52.6</v>
-      </c>
-      <c r="M16">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N16">
-        <v>57.5</v>
-      </c>
-      <c r="O16">
-        <v>60.7</v>
-      </c>
-      <c r="P16">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q16">
-        <v>58.9</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>-0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Vooropleiding</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Overig</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>4956</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Switch extern</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Overig</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
-      </c>
-      <c r="K17">
-        <v>22</v>
-      </c>
-      <c r="L17">
-        <v>52.6</v>
-      </c>
-      <c r="M17">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N17">
-        <v>57.5</v>
-      </c>
-      <c r="O17">
-        <v>60.7</v>
-      </c>
-      <c r="P17">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q17">
-        <v>58.9</v>
-      </c>
-      <c r="R17">
-        <v>-0.2</v>
-      </c>
-      <c r="S17">
-        <v>-0.1</v>
-      </c>
-      <c r="T17">
-        <v>-0.1</v>
-      </c>
-      <c r="U17">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Vooropleiding</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Onbekend</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>4956</v>
-      </c>
-      <c r="D18">
-        <v>32</v>
-      </c>
-      <c r="E18">
-        <v>0.006</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Tussenjaar</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Onbekend</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
-      </c>
-      <c r="K18">
-        <v>21</v>
-      </c>
-      <c r="L18">
-        <v>52.6</v>
-      </c>
-      <c r="M18">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="N18">
-        <v>57.5</v>
-      </c>
-      <c r="O18">
-        <v>60.7</v>
-      </c>
-      <c r="P18">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="Q18">
-        <v>58.9</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>-0</v>
-      </c>
-      <c r="T18">
-        <v>-0</v>
-      </c>
-      <c r="U18">
-        <v>2019</v>
+        <v>6.4</v>
+      </c>
+      <c r="V15">
+        <v>6.4</v>
+      </c>
+      <c r="W15">
+        <v>5.9</v>
+      </c>
+      <c r="X15">
+        <v>6.3</v>
+      </c>
+      <c r="Y15">
+        <v>7</v>
+      </c>
+      <c r="Z15">
+        <v>6.2</v>
+      </c>
+      <c r="AA15">
+        <v>0.1</v>
+      </c>
+      <c r="AB15">
+        <v>0.1</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>2015</v>
       </c>
     </row>
   </sheetData>
